--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>366205.9163936882</v>
+        <v>366206</v>
       </c>
       <c r="R2" t="n">
-        <v>6248471.751515158</v>
+        <v>6248472</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1990-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>366205.9163936882</v>
+        <v>366206</v>
       </c>
       <c r="R3" t="n">
-        <v>6248471.751515158</v>
+        <v>6248472</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1990-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,12 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366205.9163936882</v>
+        <v>366206</v>
       </c>
       <c r="R4" t="n">
-        <v>6248471.751515158</v>
+        <v>6248472</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1010,19 +975,9 @@
           <t>1990-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102819</v>
+        <v>102829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110691</v>
+        <v>110704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102890</v>
+        <v>102895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110774</v>
+        <v>110779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102895</v>
+        <v>102903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110779</v>
+        <v>110787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63314900</v>
       </c>
       <c r="B2" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63314910</v>
       </c>
       <c r="B4" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63314900</v>
+        <v>63314910</v>
       </c>
       <c r="B2" t="n">
-        <v>102913</v>
+        <v>111389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ulmus glabra/4C0d2214/Förslöv s:n/MGu/ /Mats Gustafsson,Malmö</t>
+          <t>Sanicula europaea/4C0d2214/Förslöv s:n/MGu/ /Mats Gustafsson,Malmö</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>SkFlora      4679</t>
+          <t>SkFlora      4689</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,7 +794,7 @@
         <v>63314916</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,32 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63314910</v>
+        <v>63314900</v>
       </c>
       <c r="B4" t="n">
-        <v>110797</v>
+        <v>103402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sanicula europaea/4C0d2214/Förslöv s:n/MGu/ /Mats Gustafsson,Malmö</t>
+          <t>Ulmus glabra/4C0d2214/Förslöv s:n/MGu/ /Mats Gustafsson,Malmö</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>SkFlora      4689</t>
+          <t>SkFlora      4679</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 2943-2023 artfynd.xlsx
+++ b/artfynd/A 2943-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63314910</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63314916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63314900</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>